--- a/config/futures_variety.xlsx
+++ b/config/futures_variety.xlsx
@@ -1,58 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="期货品种数据" r:id="rId3" sheetId="1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="期货品种数据" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
-      <sz val="11.0"/>
-      <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="宋体"/>
-      <sz val="14.0"/>
-      <b val="true"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
-      <patternFill patternType="darkGray"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="22"/>
-      </patternFill>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -60,2448 +42,2784 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyAlignment="true" applyBorder="true" applyFill="true" applyFont="true">
-      <alignment horizontal="center" wrapText="true" vertical="center"/>
-      <protection locked="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E89"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>tabName</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>contract</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>contractName</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>keyWords</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>能源</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>sc</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>原油</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>原油,石油</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>能源</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>fu</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>燃油</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>燃油,重油,船用油</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>能源</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>lu</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>低硫燃油</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>燃油,船用油</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>能源</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>pg</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>LPG</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>LPG,液化气,丙烷</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>能源</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>ZC</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>动煤</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>煤</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>化工</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>FG</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>玻璃</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>玻璃,平板玻璃</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>化工</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>纯碱</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>纯碱,碳酸钠</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>化工</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>SH</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>烧碱</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>烧碱,氢氧化钠</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>化工</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>bu</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>沥青</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>沥青,石油沥青</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>化工</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>甲醇</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>甲醇,木醇,煤化工</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>化工</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>TA</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>PTA</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>PTA,精对苯二甲酸</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>化工</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>PX</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>对二甲苯</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>二甲苯,PX,芳烃</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>化工</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>bz</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>纯苯</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>苯,芳烃,化工基础原料</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>化工</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>PF</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>短纤</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>短纤,短纤维</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>化工</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>eb</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>苯乙烯</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>苯乙烯,PS</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>化工</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>eg</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>乙二醇</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>乙二醇,EG,甘醇</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>化工</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>丙烯</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>丙烯,烯烃,化工原料</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>化工</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>pp</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>聚丙烯</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>丙烯,PP,聚丙</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>化工</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>v</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>PVC</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>PVC,聚氯乙烯,塑料</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>化工</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>塑料</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>塑料,PVC,聚乙烯</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>化工</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>PR</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>瓶片</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>瓶片,聚酯瓶片</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>化工</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>ru</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>天然橡胶</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>橡胶,NR</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>化工</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>br</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>合成橡胶</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>合成橡胶,丁二烯,合成胶</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>化工</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>nr</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>20号胶</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>20号胶,橡胶,标胶</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>化工</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>UR</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>尿素</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>尿素,脲,氮肥</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>化工</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>sp</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>纸浆</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>纸浆,木浆,造纸原料</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>化工</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>op</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>双胶纸</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>双胶,胶版纸</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>建材</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>rb</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>螺纹钢</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>钢</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>建材</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>FG</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>玻璃</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>玻璃,平板玻璃</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>建材</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>v</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>PVC</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>PVC,聚氯乙烯,塑料</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>建材</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>lg</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>原木</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>建材</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>bb</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>胶合板</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>胶合板,多层板</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>建材</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>fb</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>纤维板</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>纤维板,密度板</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>钢铁</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>i</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" t="inlineStr">
         <is>
           <t>铁矿石</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>铁矿</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>钢铁</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>rb</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>螺纹钢</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>钢</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>钢铁</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>hc</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>热卷</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>热卷,热轧卷板</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>钢铁</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>ss</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>不锈钢</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>不锈钢,铬镍钢</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>钢铁</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>wr</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>线材</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>线材,盘条</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>黑色产业</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>i</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>铁矿石</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>铁矿</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>黑色产业</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>rb</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>螺纹钢</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>钢</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>黑色产业</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>hc</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>热卷</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>热卷,热轧卷板</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>黑色产业</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>j</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>焦炭</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>焦炭,冶金焦</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>黑色产业</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>jm</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>焦煤</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>焦煤,主焦煤,炼焦煤</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>黑色产业</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>硅铁</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>铁,硅铁</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>黑色产业</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>SM</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>锰硅</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>锰,锰硅</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>黑色产业</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>ss</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>不锈钢</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>不锈钢,铬镍钢</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>黑色产业</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>wr</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>线材</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>线材,盘条</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+      <c r="A49" t="inlineStr">
         <is>
           <t>有色金属</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B49" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>cu</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>沪铜</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>铜,Cu</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+      <c r="A50" t="inlineStr">
         <is>
           <t>有色金属</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B50" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>al</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>沪铝</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>铝,Al</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+      <c r="A51" t="inlineStr">
         <is>
           <t>有色金属</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>ni</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>沪镍</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>镍,Ni</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+      <c r="A52" t="inlineStr">
         <is>
           <t>有色金属</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>sn</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>沪锡</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>锡,Sn</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>有色金属</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>pb</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>沪铅</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>铅,Pb</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+      <c r="A54" t="inlineStr">
         <is>
           <t>有色金属</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B54" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>zn</t>
         </is>
       </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>沪锌</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>锌,Zn</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+      <c r="A55" t="inlineStr">
         <is>
           <t>有色金属</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>ao</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>氧化铝</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>铝,矾土</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+      <c r="A56" t="inlineStr">
         <is>
           <t>有色金属</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B56" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>ad</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>铝合金</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>铝</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="A57" t="inlineStr">
         <is>
           <t>有色金属</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B57" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>bc</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>国际铜</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>铜</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+      <c r="A58" t="inlineStr">
         <is>
           <t>有色金属</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>UGFF</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>si</t>
         </is>
       </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>工业硅</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>硅</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+      <c r="A59" t="inlineStr">
         <is>
           <t>有色金属</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>UGFF</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
+      <c r="C59" t="inlineStr">
         <is>
           <t>ps</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="D59" t="inlineStr">
         <is>
           <t>多晶硅</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>多晶硅,硅料</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+      <c r="A60" t="inlineStr">
         <is>
           <t>有色金属</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>UGFF</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>lc</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>碳酸锂</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>锂</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+      <c r="A61" t="inlineStr">
         <is>
           <t>煤炭</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B61" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>j</t>
         </is>
       </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>焦炭</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>焦炭,冶金焦</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+      <c r="A62" t="inlineStr">
         <is>
           <t>煤炭</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>jm</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>焦煤</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>焦煤,主焦煤,炼焦煤</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+      <c r="A63" t="inlineStr">
         <is>
           <t>煤炭</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>ZC</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>动力煤</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>煤</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="A64" t="inlineStr">
         <is>
           <t>贵金属</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B64" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>au</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>沪金</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>沪金,金价,金银,Au</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="A65" t="inlineStr">
         <is>
           <t>贵金属</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B65" t="inlineStr">
         <is>
           <t>65</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
+      <c r="C65" t="inlineStr">
         <is>
           <t>ag</t>
         </is>
       </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="D65" t="inlineStr">
         <is>
           <t>沪银</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>沪银,银价,金银,Ag</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="A66" t="inlineStr">
         <is>
           <t>贵金属</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B66" t="inlineStr">
         <is>
           <t>UGFF</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
+      <c r="C66" t="inlineStr">
         <is>
           <t>pt</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D66" t="inlineStr">
         <is>
           <t>铂</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>铂,Pt</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="A67" t="inlineStr">
         <is>
           <t>贵金属</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>UGFF</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>pd</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>钯</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>钯,Pd</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="A68" t="inlineStr">
         <is>
           <t>油脂油料</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>y</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>豆油</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>豆油</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="A69" t="inlineStr">
         <is>
           <t>油脂油料</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
+      <c r="B69" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>p</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D69" t="inlineStr">
         <is>
           <t>棕榈油</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>棕榈,棕油</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="A70" t="inlineStr">
         <is>
           <t>油脂油料</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>OI</t>
         </is>
       </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>菜油</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>菜油,菜籽油</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="A71" t="inlineStr">
         <is>
           <t>油脂油料</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
+      <c r="B71" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>PK</t>
         </is>
       </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>花生</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>花生</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="A72" t="inlineStr">
         <is>
           <t>油脂油料</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>豆一</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>豆</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="A73" t="inlineStr">
         <is>
           <t>油脂油料</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
+      <c r="B73" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="C73" s="2" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>b</t>
         </is>
       </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="D73" t="inlineStr">
         <is>
           <t>豆二</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E73" t="inlineStr">
         <is>
           <t>豆</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="A74" t="inlineStr">
         <is>
           <t>油脂油料</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>RS</t>
         </is>
       </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>菜籽</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E74" t="inlineStr">
         <is>
           <t>菜籽</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="A75" t="inlineStr">
         <is>
           <t>谷物饲料</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B75" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
+      <c r="C75" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="D75" t="inlineStr">
         <is>
           <t>豆粕</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E75" t="inlineStr">
         <is>
           <t>豆粕</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="A76" t="inlineStr">
         <is>
           <t>谷物饲料</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B76" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
+      <c r="C76" t="inlineStr">
         <is>
           <t>RM</t>
         </is>
       </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="D76" t="inlineStr">
         <is>
           <t>菜粕</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>菜粕,菜籽粕</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="A77" t="inlineStr">
         <is>
           <t>谷物饲料</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>玉米</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>玉米,苞米</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="A78" t="inlineStr">
         <is>
           <t>谷物饲料</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B78" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C78" t="inlineStr">
         <is>
           <t>rr</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D78" t="inlineStr">
         <is>
           <t>粳米</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E78" t="inlineStr">
         <is>
           <t>米,粳</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="A79" t="inlineStr">
         <is>
           <t>谷物饲料</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
+      <c r="B79" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="C79" s="2" t="inlineStr">
+      <c r="C79" t="inlineStr">
         <is>
           <t>JR</t>
         </is>
       </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="D79" t="inlineStr">
         <is>
           <t>粳稻</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E79" t="inlineStr">
         <is>
           <t>稻</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="A80" t="inlineStr">
         <is>
           <t>谷物饲料</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B80" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C80" t="inlineStr">
         <is>
           <t>RI</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D80" t="inlineStr">
         <is>
           <t>早籼稻</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E80" t="inlineStr">
         <is>
           <t>稻</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="A81" t="inlineStr">
         <is>
           <t>谷物饲料</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="C81" s="2" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>PM</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>普麦</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E81" t="inlineStr">
         <is>
           <t>麦</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="A82" t="inlineStr">
         <is>
           <t>谷物饲料</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
+      <c r="B82" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="C82" s="2" t="inlineStr">
+      <c r="C82" t="inlineStr">
         <is>
           <t>WH</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>强麦</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>麦</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="A83" t="inlineStr">
         <is>
           <t>农副软商</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="C83" s="2" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>CF</t>
         </is>
       </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>棉花</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>棉</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="A84" t="inlineStr">
         <is>
           <t>农副软商</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="C84" s="2" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>SR</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>白糖</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>糖</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="A85" t="inlineStr">
         <is>
           <t>农副软商</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="C85" s="2" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>AP</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>苹果</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>苹</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="A86" t="inlineStr">
         <is>
           <t>农副软商</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="C86" s="2" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>lg</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>原木</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>木</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="A87" t="inlineStr">
         <is>
           <t>农副软商</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="C87" s="2" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>cs</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>玉米淀粉</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>玉米,淀粉</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="A88" t="inlineStr">
         <is>
           <t>农副软商</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>CJ</t>
         </is>
       </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>红枣</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>枣</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="A89" t="inlineStr">
         <is>
           <t>农副软商</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>67</t>
         </is>
       </c>
-      <c r="C89" s="2" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>CY</t>
         </is>
       </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>棉纱</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>纱,棉</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>